--- a/data/trans_dic/P3A$otraSIcobra-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,79</t>
+          <t>4,08; 8,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,24</t>
+          <t>5,24; 9,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,75</t>
+          <t>5,07; 7,8</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,82</t>
+          <t>2,04; 5,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,86</t>
+          <t>2,14; 4,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,34</t>
+          <t>2,29; 4,35</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,0</t>
+          <t>0,25; 1,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,4</t>
+          <t>2,0; 6,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,44</t>
+          <t>0,52; 2,55</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,45</t>
+          <t>1,5; 3,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,36</t>
+          <t>0,78; 2,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,58</t>
+          <t>1,26; 2,59</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,21</t>
+          <t>1,05; 3,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,49</t>
+          <t>1,73; 3,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,05</t>
+          <t>1,68; 3,02</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 11,68</t>
+          <t>0,61; 8,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,32</t>
+          <t>2,97; 5,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,47</t>
+          <t>2,85; 5,48</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,37</t>
+          <t>2,02; 3,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 3,85</t>
+          <t>2,68; 3,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,42</t>
+          <t>2,52; 3,4</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20912; 39378</t>
+          <t>20588; 40618</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23171; 41301</t>
+          <t>23396; 40447</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47943; 73821</t>
+          <t>48220; 74275</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9200; 21796</t>
+          <t>9219; 23390</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8095; 18601</t>
+          <t>8182; 18215</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18923; 36223</t>
+          <t>19118; 36334</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1603; 13338</t>
+          <t>1684; 12994</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3415; 10648</t>
+          <t>3335; 11145</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4812; 20399</t>
+          <t>4368; 21322</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15922; 35664</t>
+          <t>15535; 35293</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7729; 23076</t>
+          <t>7597; 22472</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26346; 51963</t>
+          <t>25432; 52090</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4777; 15254</t>
+          <t>4990; 15053</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14243; 29397</t>
+          <t>14545; 29778</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22288; 40172</t>
+          <t>22050; 39720</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2076; 28092</t>
+          <t>1474; 21459</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22448; 40472</t>
+          <t>22603; 41812</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27257; 54824</t>
+          <t>28567; 54934</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>68728; 113844</t>
+          <t>68157; 113220</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>95647; 137733</t>
+          <t>95786; 135861</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>175707; 237608</t>
+          <t>175519; 236315</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobra-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,04</t>
+          <t>4,27; 8,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,05</t>
+          <t>5,31; 9,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,8</t>
+          <t>5,28; 7,94</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,18</t>
+          <t>2,01; 5,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,76</t>
+          <t>2,48; 5,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,35</t>
+          <t>2,55; 4,5</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,94</t>
+          <t>0,94; 3,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,7</t>
+          <t>2,12; 6,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,55</t>
+          <t>1,58; 3,88</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,41</t>
+          <t>1,58; 3,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,3</t>
+          <t>1,2; 2,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,59</t>
+          <t>1,61; 2,79</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,17</t>
+          <t>0,89; 2,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,54</t>
+          <t>2,14; 3,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,02</t>
+          <t>1,83; 3,13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,92</t>
+          <t>0,44; 9,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,49</t>
+          <t>2,88; 5,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,48</t>
+          <t>2,74; 5,24</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,35</t>
+          <t>2,37; 3,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,8</t>
+          <t>3,13; 4,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,4</t>
+          <t>2,91; 3,66</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>31763</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60353</t>
+          <t>65994</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20588; 40618</t>
+          <t>23485; 44847</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23396; 40447</t>
+          <t>25901; 44533</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48220; 74275</t>
+          <t>54857; 82402</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>31814</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9219; 23390</t>
+          <t>9705; 24360</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8182; 18215</t>
+          <t>10477; 22936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19118; 36334</t>
+          <t>23134; 40809</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>16397</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1684; 12994</t>
+          <t>4424; 18007</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3335; 11145</t>
+          <t>3964; 12148</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4368; 21322</t>
+          <t>10405; 25563</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>23744</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>41907</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15535; 35293</t>
+          <t>17889; 40043</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7597; 22472</t>
+          <t>10346; 22718</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25432; 52090</t>
+          <t>32029; 55508</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>33191</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4990; 15053</t>
+          <t>5031; 15456</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14545; 29778</t>
+          <t>17808; 32782</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22050; 39720</t>
+          <t>25537; 43843</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>30600</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38573</t>
+          <t>40742</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1474; 21459</t>
+          <t>1035; 22115</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22603; 41812</t>
+          <t>24353; 43650</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28567; 54934</t>
+          <t>29678; 56723</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>99560</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>117079</t>
+          <t>130485</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208039</t>
+          <t>230045</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>68157; 113220</t>
+          <t>81457; 122377</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>95786; 135861</t>
+          <t>113841; 149700</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>175519; 236315</t>
+          <t>205681; 258906</t>
         </is>
       </c>
     </row>
